--- a/docs/design-docs/16_UIテスト難点マップ.xlsx
+++ b/docs/design-docs/16_UIテスト難点マップ.xlsx
@@ -10,7 +10,386 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>UIテスト難点マップ</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-TEST-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>目的</t>
+  </si>
+  <si>
+    <t>全画面×テスト難点カテゴリmatrix</t>
+  </si>
+  <si>
+    <t>テスト難点カテゴリ</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>カテゴリ</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>Selenium困難性</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>Stale Element</t>
+  </si>
+  <si>
+    <t>動的行追加/削除(Submit→再描画)で既存要素参照無効</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>Indexed Properties</t>
+  </si>
+  <si>
+    <t>name属性 details[{n}].field 形式</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>Wizard</t>
+  </si>
+  <si>
+    <t>multi step data持回り+戻る→修正→進む</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>条件付validation</t>
+  </si>
+  <si>
+    <t>状態により必須項目変化</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>Popup→親画面</t>
+  </si>
+  <si>
+    <t>window.open→選択→opener値反映</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>File Upload</t>
+  </si>
+  <si>
+    <t>添付file+同時validation</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>一括操作+confirm</t>
+  </si>
+  <si>
+    <t>window.confirm OK/Cancel</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>動的column</t>
+  </si>
+  <si>
+    <t>期間によりcolumn数変動</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>nest table</t>
+  </si>
+  <si>
+    <t>大分類rowspan→中分類→項目</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>印刷用別window</t>
+  </si>
+  <si>
+    <t>window.open→別window内容検証</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>CSS色分け</t>
+  </si>
+  <si>
+    <t>badge/cell色class検証</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>paging複合</t>
+  </si>
+  <si>
+    <t>頁跨操作+全選択+状態変動</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>CSV出力</t>
+  </si>
+  <si>
+    <t>download file内容検証</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>session切れ</t>
+  </si>
+  <si>
+    <t>session timeout後挙動</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>多段階遷移</t>
+  </si>
+  <si>
+    <t>未了→調査中→対応中→完了→CAPA</t>
+  </si>
+  <si>
+    <t>画面×テスト難点マトリクス</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>画面名</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>設備マスタ一覧</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>設備マスタ登録編集</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>点検項目マスタ一覧</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>点検項目マスタ登録編集</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>年間点検計画一覧</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>点検計画登録Wizard</t>
+  </si>
+  <si>
+    <t>◎</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>点検実施一覧(当日)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>点検実施入力</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>点検実施詳細修正</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>点検実施承認一覧</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>異常報告一覧</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>異常報告登録</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>異常報告詳細</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>対応指示登録</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>対応指示一覧</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>対応指示詳細完了</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>是正処置報告書</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>総合レポート</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>部署マスタ登録編集</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>担当者マスタ登録編集</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>休日カレンダー一覧</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>保守部品登録編集</t>
+  </si>
+  <si>
+    <t>凡例: ◎=高度難点(組合わせ爆発), ○=難点あり</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
